--- a/data/02_exportTest/testsExport.xlsx
+++ b/data/02_exportTest/testsExport.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,6 +473,34 @@
         </is>
       </c>
       <c r="F2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-19 11:52:18.896548</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2c9aca039b34ade067579dde2670173f</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>longdescription_fr - conditions_fr - keywords_fr - image - imagecredits - thumbnail - originalimage - accessibility - accessibility_label_fr - location_district - location_insee - location_postalcode - location_image - location_imagecredits - location_phone - location_website - location_links - location_tags - location_description_fr - location_access_fr - onlineaccesslink - age_min - age_max - contributor_email - contributor_contactnumber - contributor_contactname - contributor_contactposition - contributor_organization - category - registration - links</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>- valeurs manquantes :longdescription_fr - conditions_fr - keywords_fr - image - imagecredits - thumbnail - originalimage - accessibility - accessibility_label_fr - location_district - location_insee - location_postalcode - location_image - location_imagecredits - location_phone - location_website - location_links - location_tags - location_description_fr - location_access_fr - onlineaccesslink - age_min - age_max - contributor_email - contributor_contactnumber - contributor_contactname - contributor_contactposition - contributor_organization - category - registration - links</t>
+        </is>
+      </c>
+      <c r="F3" t="b">
         <v>0</v>
       </c>
     </row>
